--- a/artfynd/A 11192-2026 artfynd.xlsx
+++ b/artfynd/A 11192-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134074090</v>
       </c>
       <c r="B2" t="n">
-        <v>101360</v>
+        <v>101376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>134074089</v>
       </c>
       <c r="B3" t="n">
-        <v>106192</v>
+        <v>106208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11192-2026 artfynd.xlsx
+++ b/artfynd/A 11192-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134074090</v>
       </c>
       <c r="B2" t="n">
-        <v>101376</v>
+        <v>101386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>134074089</v>
       </c>
       <c r="B3" t="n">
-        <v>106208</v>
+        <v>106218</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11192-2026 artfynd.xlsx
+++ b/artfynd/A 11192-2026 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>134074089</v>
       </c>
       <c r="B3" t="n">
-        <v>106218</v>
+        <v>106219</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11192-2026 artfynd.xlsx
+++ b/artfynd/A 11192-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134074090</v>
       </c>
       <c r="B2" t="n">
-        <v>101386</v>
+        <v>101388</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>134074089</v>
       </c>
       <c r="B3" t="n">
-        <v>106219</v>
+        <v>106221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11192-2026 artfynd.xlsx
+++ b/artfynd/A 11192-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134074090</v>
       </c>
       <c r="B2" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>134074089</v>
       </c>
       <c r="B3" t="n">
-        <v>106222</v>
+        <v>106229</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11192-2026 artfynd.xlsx
+++ b/artfynd/A 11192-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134074090</v>
+        <v>134074089</v>
       </c>
       <c r="B2" t="n">
-        <v>101396</v>
+        <v>106236</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134074089</v>
+        <v>134074088</v>
       </c>
       <c r="B3" t="n">
-        <v>106229</v>
+        <v>104197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,16 +792,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221141</v>
+        <v>221987</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Skogsbingel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Mercurialis perennis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -880,6 +880,324 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134074090</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Igelsjö väster om, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>424062</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6481465</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lerdala</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Betesmark</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134074081</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99472</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Igelsjö väster om, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>424017</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6481643</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lerdala</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Betesmark</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134074083</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Igelsjö väster om, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>424017</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6481643</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lerdala</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Betesmark</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Billingens flora</t>
         </is>

--- a/artfynd/A 11192-2026 artfynd.xlsx
+++ b/artfynd/A 11192-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134074089</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134074088</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134074090</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134074081</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,8 +1227,20 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134074083</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>